--- a/stories/arbres/TREE-SOC-007.xlsx
+++ b/stories/arbres/TREE-SOC-007.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noé est dans la chambre, avec maman. Un grand livre est ouvert. Maman dit un nom : la France. Noé répète le nom. France. Sur la page, de l'eau bleue. Un paysage. La mer. Noé dit : la mer. Un nom. Un paysage. Pas de grands mots d'adultes. Un pays. Un paysage. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
+          <t>Noé est dans la chambre, avec maman. Un grand livre est ouvert. Maman dit un nom : la France. Noé répète le nom. France. Sur la page, de l'eau bleue. Un paysage. La mer. La mer. Un nom. Un paysage. Pas de grands mots d'adultes. Un pays. Un paysage. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Noé est dans la chambre, avec maman. Un grand livre est ouvert. Maman dit un nom : la France. Noé répète le nom. France. Sur la page, de l'eau bleue. Un paysage. La mer.
+enfant-m|La mer.
+narrateur|Un nom. Un paysage. Pas de grands mots d'adultes. Un pays. Un paysage. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1678,11 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Noé regarde le chat du livre. À côté, un nom : le Maroc. Un paysage : le désert. Sable. Noé dit le nom. Noé dit le paysage. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1859,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|La France, c'est un quoi ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2032,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a dit un nom. France. Noé a dit un paysage. La mer. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2223,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2390,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Noé va vers le bac à sable. La fenêtre vibre un peu. Au bac à sable, Noé fait une mer. Paysage. Maman dit un nom : France. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2529,6 +2583,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -2693,6 +2752,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton rouge. La lumière est claire. On s'assoit un moment. On a dit un nom. On a dit un paysage. La mer chante dans la tête. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2919,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3086,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton bleu. Des miettes dorment sur la table. On respire, un, deux. On a dit un nom. On a dit un paysage. La montagne est haute, tout doux. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Maman serre Noé tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3253,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3420,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton vert. Un chat miaule une fois. On referme le sac. On a dit un nom. On a dit un paysage. Le désert est calme. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3587,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3754,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Noé va vers le toboggan. Le bois sent le chaud. Au toboggan, Noé pense à la montagne. Paysage. Un nom : Suisse. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3855,6 +3949,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3879,7 +3978,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Noé pose un jeton rouge. Les chaussures font toc toc. On essuie une miette. On a dit un nom. On a dit un paysage. Le livre est rangé. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé range. Maman dit : c'est bien.</t>
+          <t>Noé pose un jeton rouge. Les chaussures font toc toc. On essuie une miette. On a dit un nom. On a dit un paysage. Le livre est rangé. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé range. C'est bien.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4017,6 +4116,12 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton rouge. Les chaussures font toc toc. On essuie une miette. On a dit un nom. On a dit un paysage. Le livre est rangé. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4284,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4451,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton bleu. La couverture est douce. On met le doudou près. On a dit un nom. On a dit un paysage. La mer chante dans la tête. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. On souffle. Noé sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4618,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4785,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton vert. Une cloche tinte au loin. On lace les chaussures. On a dit un nom. On a dit un paysage. La montagne est haute, tout doux. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4952,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5119,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Noé va vers les balançoires. Le lait est froid dans le verre. Aux balançoires, Noé dit mer. Paysage. Un nom : Italie. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5177,6 +5312,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -5341,6 +5481,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton rouge. Le bois sent le chaud. On met le manteau. On a dit un nom. On a dit un paysage. Le désert est calme. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5648,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5815,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton bleu. Une goutte tombe, ploc. On boit une gorgée. On a dit un nom. On a dit un paysage. Le livre est rangé. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Maman serre Noé tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5982,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6149,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton vert. Le savon sent la fleur. On feuillette le livre. On a dit un nom. On a dit un paysage. La mer chante dans la tête. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6316,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6313,6 +6483,11 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Noé regarde le chien. Maman dit un nom : l'Italie. Un paysage : la mer. Noé répète. Nom. Paysage. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6664,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|L'eau bleue, c'est un quoi ?</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6837,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Nom. Paysage. Noé a vu la mer et la montagne. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7028,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7005,6 +7195,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Noé va vers le bac à sable. Une pomme sent le sucré. Le sable est un désert. Paysage. Un nom : Maroc. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7195,6 +7390,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7219,7 +7419,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Noé pose un jeton rouge. Le tissu est tout doux. On referme le livre. On a dit un nom. On a dit un paysage. La montagne est haute, tout doux. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé range. Maman dit : c'est bien.</t>
+          <t>Noé pose un jeton rouge. Le tissu est tout doux. On referme le livre. On a dit un nom. On a dit un paysage. La montagne est haute, tout doux. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé range. C'est bien.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7357,6 +7557,12 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton rouge. Le tissu est tout doux. On referme le livre. On a dit un nom. On a dit un paysage. La montagne est haute, tout doux. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7519,6 +7725,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7681,6 +7892,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton bleu. Une cuillère tinte. On pose le ballon. On a dit un nom. On a dit un paysage. Le désert est calme. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. On souffle. Noé sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7843,6 +8059,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8005,6 +8226,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton vert. Le sable est tiède. On secoue le sable. On a dit un nom. On a dit un paysage. Le livre est rangé. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8167,6 +8393,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8329,6 +8560,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Noé va vers le toboggan. Un rire court, tout petit. Noé glisse. Montagne. Paysage. Maman dit le nom. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8517,6 +8753,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -8681,6 +8922,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton rouge. Un rire court, tout petit. On caresse le tissu. On a dit un nom. On a dit un paysage. La mer chante dans la tête. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8843,6 +9089,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9005,6 +9256,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton bleu. Le papier froisse, chut. On tend la main. On a dit un nom. On a dit un paysage. La montagne est haute, tout doux. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Maman serre Noé tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9167,6 +9423,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9329,6 +9590,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton vert. L'herbe chatouille le mollet. On chante un petit air. On a dit un nom. On a dit un paysage. Le désert est calme. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9491,6 +9757,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9653,6 +9924,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Noé va vers les balançoires. Le sable est tiède. La balançoire va. Noé dit un nom. Noé dit un paysage. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9843,6 +10119,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9867,7 +10148,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Noé pose un jeton rouge. Un pigeon roucoule. On compte jusqu'à trois. On a dit un nom. On a dit un paysage. Le livre est rangé. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé range. Maman dit : c'est bien.</t>
+          <t>Noé pose un jeton rouge. Un pigeon roucoule. On compte jusqu'à trois. On a dit un nom. On a dit un paysage. Le livre est rangé. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé range. C'est bien.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10005,6 +10286,12 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton rouge. Un pigeon roucoule. On compte jusqu'à trois. On a dit un nom. On a dit un paysage. Le livre est rangé. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10167,6 +10454,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10329,6 +10621,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton bleu. La fenêtre vibre un peu. On montre du doigt. On a dit un nom. On a dit un paysage. La mer chante dans la tête. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. On souffle. Noé sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10491,6 +10788,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10653,6 +10955,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton vert. Le lait est froid dans le verre. On range la chaise. On a dit un nom. On a dit un paysage. La montagne est haute, tout doux. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10815,6 +11122,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10839,7 +11151,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Noé regarde la poule. Maman dit un nom : la Suisse. Un paysage : la montagne. Noé dit : montagne. Nom. Paysage. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
+          <t>Noé regarde la poule. Maman dit un nom : la Suisse. Un paysage : la montagne. Montagne. Nom. Paysage. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10977,6 +11289,12 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Noé regarde la poule. Maman dit un nom : la Suisse. Un paysage : la montagne.
+enfant-m|Montagne. Nom. Paysage. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11153,6 +11471,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|La montagne, c'est un quoi ?</t>
         </is>
       </c>
     </row>
@@ -11321,6 +11644,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Un pays, un paysage. Maman ferme le livre doucement. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11507,6 +11835,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11669,6 +12002,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Noé va vers le bac à sable. Un oiseau chante tout près. Noé creuse. Mer. Paysage. Nom de pays. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11857,6 +12195,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -12021,6 +12364,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton rouge. La corde du sac est rêche. On range un objet. On a dit un nom. On a dit un paysage. Le désert est calme. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12183,6 +12531,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12345,6 +12698,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton bleu. Le savon mousse entre les doigts. On se tient la main. On a dit un nom. On a dit un paysage. Le livre est rangé. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Maman serre Noé tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12507,6 +12865,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12669,6 +13032,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton vert. Un ruisseau chante. On dit merci. On a dit un nom. On a dit un paysage. La mer chante dans la tête. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12831,6 +13199,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12993,6 +13366,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Noé va vers le toboggan. Le savon mousse entre les doigts. En haut, maman tient la main. Nom. Paysage. Montagne. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13183,6 +13561,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13207,7 +13590,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Noé pose un jeton rouge. La laine gratte un peu. On souffle doucement. On a dit un nom. On a dit un paysage. La montagne est haute, tout doux. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé range. Maman dit : c'est bien.</t>
+          <t>Noé pose un jeton rouge. La laine gratte un peu. On souffle doucement. On a dit un nom. On a dit un paysage. La montagne est haute, tout doux. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé range. C'est bien.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13345,6 +13728,12 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton rouge. La laine gratte un peu. On souffle doucement. On a dit un nom. On a dit un paysage. La montagne est haute, tout doux. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13507,6 +13896,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13669,6 +14063,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton bleu. Un pain croustille. On écoute jusqu'au bout. On a dit un nom. On a dit un paysage. Le désert est calme. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. On souffle. Noé sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13831,6 +14230,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13993,6 +14397,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton vert. Le savon glisse. On attend son tour. On a dit un nom. On a dit un paysage. Le livre est rangé. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14155,6 +14564,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14317,6 +14731,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Noé va vers les balançoires. Un chat miaule une fois. Noé s'arrête. Maman répète un nom et un paysage. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14505,6 +14924,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -14669,6 +15093,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton rouge. Une plume vole. On sourit ensemble. On a dit un nom. On a dit un paysage. La mer chante dans la tête. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14831,6 +15260,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14993,6 +15427,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton bleu. Le banc est lisse. On pose les pieds par terre. On a dit un nom. On a dit un paysage. La montagne est haute, tout doux. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Maman serre Noé tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15155,6 +15594,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15317,6 +15761,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton vert. Un grelot sonne. On parle tout bas. On a dit un nom. On a dit un paysage. Le désert est calme. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15479,6 +15928,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15497,7 +15951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15570,6 +16024,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SOC-007.xlsx
+++ b/stories/arbres/TREE-SOC-007.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Un nom. Un paysage. Pas de grands mots d'adultes. Un pays. Un paysage. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,11 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -1683,6 +1694,7 @@
           <t>narrateur|Noé regarde le chat du livre. À côté, un nom : le Maroc. Un paysage : le désert. Sable. Noé dit le nom. Noé dit le paysage. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1866,6 +1878,7 @@
           <t>narrateur|La France, c'est un quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2037,6 +2050,7 @@
           <t>narrateur|Noé a dit un nom. France. Noé a dit un paysage. La mer. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2228,6 +2242,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2395,6 +2410,7 @@
           <t>narrateur|Noé va vers le bac à sable. La fenêtre vibre un peu. Au bac à sable, Noé fait une mer. Paysage. Maman dit un nom : France. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2590,6 +2606,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2757,6 +2774,7 @@
           <t>narrateur|Noé pose un jeton rouge. La lumière est claire. On s'assoit un moment. On a dit un nom. On a dit un paysage. La mer chante dans la tête. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2924,6 +2942,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3091,6 +3110,7 @@
           <t>narrateur|Noé pose un jeton bleu. Des miettes dorment sur la table. On respire, un, deux. On a dit un nom. On a dit un paysage. La montagne est haute, tout doux. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Maman serre Noé tout doux.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3258,6 +3278,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3425,6 +3446,7 @@
           <t>narrateur|Noé pose un jeton vert. Un chat miaule une fois. On referme le sac. On a dit un nom. On a dit un paysage. Le désert est calme. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3592,6 +3614,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3759,6 +3782,7 @@
           <t>narrateur|Noé va vers le toboggan. Le bois sent le chaud. Au toboggan, Noé pense à la montagne. Paysage. Un nom : Suisse. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3954,6 +3978,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4122,6 +4147,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4289,6 +4315,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4456,6 +4483,7 @@
           <t>narrateur|Noé pose un jeton bleu. La couverture est douce. On met le doudou près. On a dit un nom. On a dit un paysage. La mer chante dans la tête. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. On souffle. Noé sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4623,6 +4651,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4790,6 +4819,7 @@
           <t>narrateur|Noé pose un jeton vert. Une cloche tinte au loin. On lace les chaussures. On a dit un nom. On a dit un paysage. La montagne est haute, tout doux. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4957,6 +4987,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5124,6 +5155,7 @@
           <t>narrateur|Noé va vers les balançoires. Le lait est froid dans le verre. Aux balançoires, Noé dit mer. Paysage. Un nom : Italie. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5319,6 +5351,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5486,6 +5519,7 @@
           <t>narrateur|Noé pose un jeton rouge. Le bois sent le chaud. On met le manteau. On a dit un nom. On a dit un paysage. Le désert est calme. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5653,6 +5687,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5820,6 +5855,7 @@
           <t>narrateur|Noé pose un jeton bleu. Une goutte tombe, ploc. On boit une gorgée. On a dit un nom. On a dit un paysage. Le livre est rangé. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Maman serre Noé tout doux.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5987,6 +6023,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6154,6 +6191,7 @@
           <t>narrateur|Noé pose un jeton vert. Le savon sent la fleur. On feuillette le livre. On a dit un nom. On a dit un paysage. La mer chante dans la tête. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6321,6 +6359,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6488,6 +6527,11 @@
           <t>narrateur|Noé regarde le chien. Maman dit un nom : l'Italie. Un paysage : la mer. Noé répète. Nom. Paysage. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6671,6 +6715,7 @@
           <t>narrateur|L'eau bleue, c'est un quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6842,6 +6887,7 @@
           <t>narrateur|Nom. Paysage. Noé a vu la mer et la montagne. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7033,6 +7079,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7200,6 +7247,7 @@
           <t>narrateur|Noé va vers le bac à sable. Une pomme sent le sucré. Le sable est un désert. Paysage. Un nom : Maroc. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7395,6 +7443,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7563,6 +7612,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7730,6 +7780,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7897,6 +7948,7 @@
           <t>narrateur|Noé pose un jeton bleu. Une cuillère tinte. On pose le ballon. On a dit un nom. On a dit un paysage. Le désert est calme. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. On souffle. Noé sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8064,6 +8116,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8231,6 +8284,7 @@
           <t>narrateur|Noé pose un jeton vert. Le sable est tiède. On secoue le sable. On a dit un nom. On a dit un paysage. Le livre est rangé. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8398,6 +8452,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8565,6 +8620,7 @@
           <t>narrateur|Noé va vers le toboggan. Un rire court, tout petit. Noé glisse. Montagne. Paysage. Maman dit le nom. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8760,6 +8816,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8927,6 +8984,7 @@
           <t>narrateur|Noé pose un jeton rouge. Un rire court, tout petit. On caresse le tissu. On a dit un nom. On a dit un paysage. La mer chante dans la tête. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9094,6 +9152,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9261,6 +9320,7 @@
           <t>narrateur|Noé pose un jeton bleu. Le papier froisse, chut. On tend la main. On a dit un nom. On a dit un paysage. La montagne est haute, tout doux. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Maman serre Noé tout doux.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9428,6 +9488,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9595,6 +9656,7 @@
           <t>narrateur|Noé pose un jeton vert. L'herbe chatouille le mollet. On chante un petit air. On a dit un nom. On a dit un paysage. Le désert est calme. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9762,6 +9824,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9929,6 +9992,7 @@
           <t>narrateur|Noé va vers les balançoires. Le sable est tiède. La balançoire va. Noé dit un nom. Noé dit un paysage. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10124,6 +10188,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10292,6 +10357,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10459,6 +10525,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10626,6 +10693,7 @@
           <t>narrateur|Noé pose un jeton bleu. La fenêtre vibre un peu. On montre du doigt. On a dit un nom. On a dit un paysage. La mer chante dans la tête. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. On souffle. Noé sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10793,6 +10861,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10960,6 +11029,7 @@
           <t>narrateur|Noé pose un jeton vert. Le lait est froid dans le verre. On range la chaise. On a dit un nom. On a dit un paysage. La montagne est haute, tout doux. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11127,6 +11197,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11295,6 +11366,7 @@
 enfant-m|Montagne. Nom. Paysage. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11478,6 +11550,7 @@
           <t>narrateur|La montagne, c'est un quoi ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11649,6 +11722,7 @@
           <t>narrateur|Un pays, un paysage. Maman ferme le livre doucement. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11840,6 +11914,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12007,6 +12082,7 @@
           <t>narrateur|Noé va vers le bac à sable. Un oiseau chante tout près. Noé creuse. Mer. Paysage. Nom de pays. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12202,6 +12278,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12369,6 +12446,7 @@
           <t>narrateur|Noé pose un jeton rouge. La corde du sac est rêche. On range un objet. On a dit un nom. On a dit un paysage. Le désert est calme. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12536,6 +12614,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12703,6 +12782,7 @@
           <t>narrateur|Noé pose un jeton bleu. Le savon mousse entre les doigts. On se tient la main. On a dit un nom. On a dit un paysage. Le livre est rangé. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Maman serre Noé tout doux.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12870,6 +12950,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13037,6 +13118,7 @@
           <t>narrateur|Noé pose un jeton vert. Un ruisseau chante. On dit merci. On a dit un nom. On a dit un paysage. La mer chante dans la tête. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13204,6 +13286,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13371,6 +13454,7 @@
           <t>narrateur|Noé va vers le toboggan. Le savon mousse entre les doigts. En haut, maman tient la main. Nom. Paysage. Montagne. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13566,6 +13650,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13734,6 +13819,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13901,6 +13987,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14068,6 +14155,7 @@
           <t>narrateur|Noé pose un jeton bleu. Un pain croustille. On écoute jusqu'au bout. On a dit un nom. On a dit un paysage. Le désert est calme. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. On souffle. Noé sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14235,6 +14323,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14402,6 +14491,7 @@
           <t>narrateur|Noé pose un jeton vert. Le savon glisse. On attend son tour. On a dit un nom. On a dit un paysage. Le livre est rangé. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14569,6 +14659,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14736,6 +14827,7 @@
           <t>narrateur|Noé va vers les balançoires. Un chat miaule une fois. Noé s'arrête. Maman répète un nom et un paysage. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14931,6 +15023,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15098,6 +15191,7 @@
           <t>narrateur|Noé pose un jeton rouge. Une plume vole. On sourit ensemble. On a dit un nom. On a dit un paysage. La mer chante dans la tête. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15265,6 +15359,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15432,6 +15527,7 @@
           <t>narrateur|Noé pose un jeton bleu. Le banc est lisse. On pose les pieds par terre. On a dit un nom. On a dit un paysage. La montagne est haute, tout doux. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Maman serre Noé tout doux.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15599,6 +15695,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15766,6 +15863,7 @@
           <t>narrateur|Noé pose un jeton vert. Un grelot sonne. On parle tout bas. On a dit un nom. On a dit un paysage. Le désert est calme. On dit un nom de pays. On dit un paysage. Mer, montagne ou désert. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15933,6 +16031,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15951,7 +16050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16031,6 +16130,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16045,7 +16158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16232,6 +16345,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
